--- a/out/Attention-MambaAMT_repeat_1_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_1_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.829132276861947</v>
+        <v>3.00677127013091</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.2927231521932763</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.581772643840161</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.229132276861947</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.2927231521932763</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.829132276861947</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.2927231521932763</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.2927231521932763</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.581772643840161</v>
+        <v>3.00677127013091</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.229132276861947</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.229132276861947</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.829132276861947</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.829132276861947</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.829132276861947</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.581772643840161</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.581772643840161</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.581772643840161</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.581772643840161</v>
+        <v>3.00677127013091</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002815703869060381</v>
+        <v>-0.0004451447031599236</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3624028107634503</v>
+        <v>0.5729356976083116</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7254918838551936</v>
+        <v>1.146956087039027</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08369380214019653</v>
+        <v>-0.1323144992944038</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.229132276861947</v>
+        <v>3.00677127013091</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2784274382363476</v>
+        <v>0.4401760536107477</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.581772643840161</v>
+        <v>3.00677127013091</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2784274382363476</v>
+        <v>0.4401760536107477</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.829132276861947</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2784274382363476</v>
+        <v>0.4395942899359258</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>1.787303664418976</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9817726438401608</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2782158495317686</v>
+        <v>4.017760883297024</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.1974250379754839</v>
+        <v>0.3419804174679189</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9817726438401608</v>
+        <v>3.60677127013091</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.08079081155628479</v>
+        <v>2.911809633251323</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.5990111339644872</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.08079081155628479</v>
+        <v>3.768019431229994</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.3280405335929329</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.08061257365747355</v>
+        <v>3.824572617598855</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.05122172427118685</v>
+        <v>0.1354853209111004</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.02939084938628657</v>
+        <v>3.767159231089726</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.1688035737084341</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.0291808949727742</v>
+        <v>3.969303404643376</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03834219728898181</v>
+        <v>0.1016409655370606</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.106238493802024</v>
+        <v>4.003668394194668</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.07849020198318717</v>
+        <v>0.07727445777129825</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2247791111716956</v>
+        <v>4.056533527547137</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02924721289541994</v>
+        <v>0.03417948816431111</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2046311161851646</v>
+        <v>4.047548093847389</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.03711793940474115</v>
+        <v>0.02712042053464228</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.249593114680896</v>
+        <v>4.067599660554325</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01830979178194343</v>
+        <v>0.01344796085605454</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2490452495151064</v>
+        <v>4.067354537835313</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0116127119468929</v>
+        <v>0.007817840804997835</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.253940964186369</v>
+        <v>4.06953556126092</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.005804086169999968</v>
+        <v>0.003907875002871733</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2539250434001549</v>
+        <v>4.069525689467401</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.002846508977838194</v>
+        <v>0.001926763565120504</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2538103461781547</v>
+        <v>4.069471754219058</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.00177080605693763</v>
+        <v>0.00111645133337532</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2545012767668993</v>
+        <v>4.069777340694825</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0004660606641668925</v>
+        <v>0.0003699709791472805</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2536605316108617</v>
+        <v>4.069398806134108</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0002325039374522157</v>
+        <v>0.0001836464563707676</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2536602172811352</v>
+        <v>4.069395907386327</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0001325900371128294</v>
+        <v>9.774023746455726e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2536928511367941</v>
+        <v>4.06940783350885</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>6.022228144858818e-05</v>
+        <v>4.47737893862285e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2536804811668538</v>
+        <v>4.069399498441807</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>4.12414819502485e-05</v>
+        <v>2.700120820192495e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2537012982944292</v>
+        <v>4.069406331291946</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.414028338497327e-05</v>
+        <v>7.887479732251461e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2536882891311454</v>
+        <v>4.069397662037255</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>6.850612186843965e-06</v>
+        <v>3.872723086529542e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2536878334702228</v>
+        <v>4.069394934206793</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>1.609447241729181e-06</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2536841915336668</v>
+        <v>4.069390615215643</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-2.707014202979226e-06</v>
+        <v>-1.724541871943372e-06</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2536794573054288</v>
+        <v>4.069385791042754</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>-3.563918267525618e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2536727384055911</v>
+        <v>4.06938493310917</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2536729667266258</v>
+        <v>4.069385161430204</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2536721710624141</v>
+        <v>4.069384365765993</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2536722333317872</v>
+        <v>4.069384428035366</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.253672261007064</v>
+        <v>4.069384455710642</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2536724132210873</v>
+        <v>4.069384607924666</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2536720672801256</v>
+        <v>4.069384261983704</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2536721433871372</v>
+        <v>4.069384338090715</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2536723094387988</v>
+        <v>4.069384504142376</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2536726692173988</v>
+        <v>4.069384863920978</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2536726899738566</v>
+        <v>4.069384884677435</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.253672793756145</v>
+        <v>4.069384988459723</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2536730220771797</v>
+        <v>4.069385216780757</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2536728975384335</v>
+        <v>4.069385092242012</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2536729252137104</v>
+        <v>4.069385119917288</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2536729805642643</v>
+        <v>4.069385175267842</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2536732434793951</v>
+        <v>4.069385438182973</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2536731604535643</v>
+        <v>4.069385355157142</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2536729528889875</v>
+        <v>4.069385147592566</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2536729667266258</v>
+        <v>4.069385161430204</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2536731051030106</v>
+        <v>4.069385299806588</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2536728214314219</v>
+        <v>4.069385016135</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2536726484609412</v>
+        <v>4.069384843164519</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2536725446786526</v>
+        <v>4.06938473938223</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2536726899738566</v>
+        <v>4.069384884677435</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2536729321325298</v>
+        <v>4.069385126836108</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2536727591620488</v>
+        <v>4.069384953865627</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2536724616528219</v>
+        <v>4.0693846563564</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2536724478151833</v>
+        <v>4.069384642518761</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2536720811177641</v>
+        <v>4.069384275821342</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2536720811177641</v>
+        <v>4.069384275821342</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.253672018848391</v>
+        <v>4.069384213551969</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2536719150661025</v>
+        <v>4.069384109769681</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2536717420956218</v>
+        <v>4.0693839367992</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2536717905273563</v>
+        <v>4.069383985230934</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2536714307487563</v>
+        <v>4.069383625452334</v>
       </c>
     </row>
     <row r="109">
@@ -87588,21 +87588,21 @@
         <v>0</v>
       </c>
       <c r="IY109" t="n">
-        <v>-4.911469014191316e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2536663878221765</v>
+        <v>4.069383583939419</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2534268348508864</v>
+        <v>4.069383639289973</v>
       </c>
     </row>
     <row r="111">
@@ -89178,21 +89178,21 @@
         <v>0</v>
       </c>
       <c r="IY111" t="n">
-        <v>0.0207495702093077</v>
+        <v>0</v>
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.274176405060194</v>
+        <v>4.069383694640527</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2738602982414979</v>
+        <v>4.069383736153442</v>
       </c>
     </row>
     <row r="113">
@@ -90768,21 +90768,21 @@
         <v>0</v>
       </c>
       <c r="IY113" t="n">
-        <v>-0.1289953556388291</v>
+        <v>0</v>
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1448649426026687</v>
+        <v>4.069383466319492</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1448649426026687</v>
+        <v>4.069383521670046</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1445787860444277</v>
+        <v>4.06938366696525</v>
       </c>
     </row>
     <row r="116">
@@ -93153,21 +93153,21 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>-0.01653468949408034</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1280440965503473</v>
+        <v>4.069383632371154</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1277606547234524</v>
+        <v>4.069383618533515</v>
       </c>
     </row>
     <row r="118">
@@ -94743,21 +94743,21 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.00132153324900315</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1697782744885497</v>
+        <v>4.069383708478165</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.09179858242800018</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3132297862152213</v>
+        <v>4.06938402674385</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.02558181492570658</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2722891191636904</v>
+        <v>4.06938384685455</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0.0151352316499641</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2768590855243679</v>
+        <v>4.069383888367466</v>
       </c>
     </row>
     <row r="122">
@@ -97923,21 +97923,21 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>0.004585853890286187</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2661836708664126</v>
+        <v>4.069383701559346</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2659353042654442</v>
+        <v>4.069383770747539</v>
       </c>
     </row>
     <row r="124">
@@ -99513,21 +99513,21 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>-0.07365938373080584</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1922759205346382</v>
+        <v>4.069383570101781</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1922759205346382</v>
+        <v>4.069383611614696</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8927231521932764</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1922759205346382</v>
+        <v>4.069383639289973</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_1_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.8885478469910492</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.8885478469910492</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.8885478469910492</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002815703869060381</v>
+        <v>-0.0002192578956338111</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3624028107634503</v>
+        <v>0.2822019910489031</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7254918838551936</v>
+        <v>0.5649380440119112</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08369380214019653</v>
+        <v>-0.06517203914661432</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.229132276861947</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2784274382363476</v>
+        <v>0.2168106940066549</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2784274382363476</v>
+        <v>0.2168106940066549</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2784274382363476</v>
+        <v>0.2166688694093737</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.4357156728880722</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2782158495317686</v>
+        <v>1.088968152113664</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.1974250379754839</v>
+        <v>0.08336934661058371</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.08079081155628479</v>
+        <v>0.819355005681348</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.1460293171779899</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.08079081155628479</v>
+        <v>1.028085160439327</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.079970729918521</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.08061257365747355</v>
+        <v>1.041871911611568</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.05122172427118685</v>
+        <v>0.0330292729044115</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.02939084938628657</v>
+        <v>1.027875416224898</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.04115114923758346</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.0291808949727742</v>
+        <v>1.077154967267476</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03834219728898181</v>
+        <v>0.02477889802482809</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.106238493802024</v>
+        <v>1.085532707437845</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.07849020198318717</v>
+        <v>0.01883862376672046</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2247791111716956</v>
+        <v>1.098420468620204</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02924721289541994</v>
+        <v>0.008329247591807724</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2046311161851646</v>
+        <v>1.096227645111195</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.03711793940474115</v>
+        <v>0.006608239374351335</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.581772643840161</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.249593114680896</v>
+        <v>1.101113409843483</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01830979178194343</v>
+        <v>0.003274440625192917</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2490452495151064</v>
+        <v>1.101049859211066</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0116127119468929</v>
+        <v>0.001903435689132979</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.253940964186369</v>
+        <v>1.101578055038964</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.005804086169999968</v>
+        <v>0.0009492178445664895</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2539250434001549</v>
+        <v>1.101571866973333</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.002846508977838194</v>
+        <v>0.0004664422986305992</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2538103461781547</v>
+        <v>1.101554932885094</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.00177080605693763</v>
+        <v>0.0002686875277880244</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2545012767668993</v>
+        <v>1.101625617644082</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0004660606641668925</v>
+        <v>8.651077467284822e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2536605316108617</v>
+        <v>1.101529727587325</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0002325039374522157</v>
+        <v>3.991582294542086e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2536602172811352</v>
+        <v>1.101525238428435</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0001325900371128294</v>
+        <v>1.946196130108506e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2536928511367941</v>
+        <v>1.101524421330565</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>6.022228144858818e-05</v>
+        <v>6.850902234816308e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2536804811668538</v>
+        <v>1.101518569280689</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>4.12414819502485e-05</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2537012982944292</v>
+        <v>1.101516796421636</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.414028338497327e-05</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2536882891311454</v>
+        <v>1.10151079688804</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>6.850612186843965e-06</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2536878334702228</v>
+        <v>1.101506554277886</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>1.609447241729181e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2536841915336668</v>
+        <v>1.101506782598921</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-2.707014202979226e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2536794573054288</v>
+        <v>1.101506872543571</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>-3.563918267525618e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2536727384055911</v>
+        <v>1.101506014609986</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9817726438401608</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2536729667266258</v>
+        <v>1.101506242931021</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2536721710624141</v>
+        <v>1.101505447266809</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2536722333317872</v>
+        <v>1.101505509536182</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.253672261007064</v>
+        <v>1.101505537211459</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2536724132210873</v>
+        <v>1.101505689425482</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2536720672801256</v>
+        <v>1.10150534348452</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2536721433871372</v>
+        <v>1.101505419591532</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2536723094387988</v>
+        <v>1.101505585643193</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.581772643840161</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2536726692173988</v>
+        <v>1.101505945421793</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2536726899738566</v>
+        <v>1.101505966178251</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.253672793756145</v>
+        <v>1.101506069960539</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2536730220771797</v>
+        <v>1.101506298281574</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2536728975384335</v>
+        <v>1.101506173742828</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2536729252137104</v>
+        <v>1.101506201418105</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2536729805642643</v>
+        <v>1.101506256768659</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9817726438401608</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2536732434793951</v>
+        <v>1.101506519683789</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2536731604535643</v>
+        <v>1.101506436657959</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2536729528889875</v>
+        <v>1.101506229093382</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2536729667266258</v>
+        <v>1.101506242931021</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2536731051030106</v>
+        <v>1.101506381307405</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2536728214314219</v>
+        <v>1.101506097635816</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2536726484609412</v>
+        <v>1.101505924665336</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2536725446786526</v>
+        <v>1.101505820883047</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2536726899738566</v>
+        <v>1.101505966178251</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2536729321325298</v>
+        <v>1.101506208336924</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2536727591620488</v>
+        <v>1.101506035366443</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2536724616528219</v>
+        <v>1.101505737857216</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2536724478151833</v>
+        <v>1.101505724019578</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2536720811177641</v>
+        <v>1.101505357322158</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.8389298129189675</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2536720811177641</v>
+        <v>1.101505357322158</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.253672018848391</v>
+        <v>1.101505295052785</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2536719150661025</v>
+        <v>1.101505191270497</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2536717420956218</v>
+        <v>1.101505018300016</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2536717905273563</v>
+        <v>1.101505066731751</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9817726438401608</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2536714307487563</v>
+        <v>1.101504706953151</v>
       </c>
     </row>
     <row r="109">
@@ -87588,21 +87588,21 @@
         <v>0</v>
       </c>
       <c r="IY109" t="n">
-        <v>-4.911469014191316e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2536663878221765</v>
+        <v>1.101504665440235</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2534268348508864</v>
+        <v>1.101504720790789</v>
       </c>
     </row>
     <row r="111">
@@ -89178,21 +89178,21 @@
         <v>0</v>
       </c>
       <c r="IY111" t="n">
-        <v>0.0207495702093077</v>
+        <v>0</v>
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.274176405060194</v>
+        <v>1.101504776141343</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.581772643840161</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2738602982414979</v>
+        <v>1.101504817654259</v>
       </c>
     </row>
     <row r="113">
@@ -90768,21 +90768,21 @@
         <v>0</v>
       </c>
       <c r="IY113" t="n">
-        <v>-0.1289953556388291</v>
+        <v>0</v>
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1448649426026687</v>
+        <v>1.101504547820308</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.229132276861947</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1448649426026687</v>
+        <v>1.101504603170862</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.581772643840161</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1445787860444277</v>
+        <v>1.101504748466066</v>
       </c>
     </row>
     <row r="116">
@@ -93153,21 +93153,21 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>-0.01653468949408034</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.829132276861947</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1280440965503473</v>
+        <v>1.10150471387197</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.581772643840161</v>
+        <v>0.1964372596156286</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1277606547234524</v>
+        <v>1.101504700034331</v>
       </c>
     </row>
     <row r="118">
@@ -94743,21 +94743,21 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.00132153324900315</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.581772643840161</v>
+        <v>1.038929812918968</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1697782744885497</v>
+        <v>1.101504789978981</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.09179858242800018</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.581772643840161</v>
+        <v>0.3964372596156286</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3132297862152213</v>
+        <v>1.101505108244666</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.02558181492570658</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.229132276861947</v>
+        <v>-0.2460552936877103</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2722891191636904</v>
+        <v>1.101504928355366</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0.0151352316499641</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2768590855243679</v>
+        <v>1.101504969868281</v>
       </c>
     </row>
     <row r="122">
@@ -97923,21 +97923,21 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>0.004585853890286187</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2661836708664126</v>
+        <v>1.101504783060162</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9817726438401608</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2659353042654442</v>
+        <v>1.101504852248354</v>
       </c>
     </row>
     <row r="124">
@@ -99513,21 +99513,21 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>-0.07365938373080584</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.829132276861947</v>
+        <v>-0.4460552936877104</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1922759205346382</v>
+        <v>1.101504651602597</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1922759205346382</v>
+        <v>1.101504693115512</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.829132276861947</v>
+        <v>-1.088547846991049</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1922759205346382</v>
+        <v>1.101504720790789</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_1_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_1_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02909659594297409</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01293106097728014</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.01141851115971804</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.01252209488302469</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.004615661688148975</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.02057011425495148</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.010015525855124</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.007229299284517765</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.01231773663312197</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.007723557762801647</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.01737706363201141</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.01132192183285952</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.01390732545405626</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.01181239169090986</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.01084400620311499</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.009860671125352383</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.01519914995878935</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.01052193064242601</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.01021775510162115</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01540972385555506</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.008024231530725956</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.01605420559644699</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.005399935878813267</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.01608939468860626</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.01022576633840799</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.007494457997381687</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.03082143887877464</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.01891330257058144</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.01009602379053831</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8885478469910492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.01091581117361784</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8885478469910492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.01081143226474524</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.007885308004915714</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.006883925758302212</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4460552936877104</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01139139477163553</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.005386772565543652</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.004502835683524609</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8885478469910492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.001689109019935131</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.007349713705480099</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.088547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0001674415543675423</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4460552936877104</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.006891281343996525</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.009654980152845383</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.038929812918968</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.006240320857614279</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.038929812918968</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.02225223742425442</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.038929812918968</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002192578956338111</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2822019910489031</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.02920478954911232</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.3964372596156286</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.5649380440119112</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.06517203914661432</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.004878200590610504</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.3964372596156286</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2168106940066549</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.002576719038188457</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2168106940066549</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.002206972800195217</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2166688694093737</v>
+        <v>0.1805353231967278</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.4357156728880722</v>
+        <v>0.2282159622144663</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01157565228641033</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.088968152113664</v>
+        <v>0.6374220041313774</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.08336934661058371</v>
+        <v>0.04366655291131923</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.007878675125539303</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.16</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.819355005681348</v>
+        <v>0.4962059105595811</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1460293171779899</v>
+        <v>0.07648632621329152</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.001280537806451321</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.028085160439327</v>
+        <v>0.6055332909506734</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.079970729918521</v>
+        <v>0.04188645735538458</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01781579107046127</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.16</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.041871911611568</v>
+        <v>0.6127544298176431</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0330292729044115</v>
+        <v>0.01729971689228928</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01176394615322351</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.027875416224898</v>
+        <v>0.6054234131568402</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04115114923758346</v>
+        <v>0.02155396268611361</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.02749829366803169</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4460552936877104</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.077154967267476</v>
+        <v>0.6312351134164363</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02477889802482809</v>
+        <v>0.01297810855661497</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.01093243900686502</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.085532707437845</v>
+        <v>0.6356225115857507</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01883862376672046</v>
+        <v>0.009865561962379997</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.0535917617380619</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4460552936877104</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.098420468620204</v>
+        <v>0.6423710901332695</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.008329247591807724</v>
+        <v>0.004360785304099126</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.03522187471389771</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1964372596156286</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.096227645111195</v>
+        <v>0.641220136472065</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.006608239374351335</v>
+        <v>0.0034579968195974</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01892923936247826</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1964372596156286</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.101113409843483</v>
+        <v>0.6437766111456487</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003274440625192917</v>
+        <v>0.001713516940890567</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.06052700057625771</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.038929812918968</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.101049859211066</v>
+        <v>0.6437409398834182</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001903435689132979</v>
+        <v>0.0009928558557509325</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.03035654500126839</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.038929812918968</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.101578055038964</v>
+        <v>0.6440151379854742</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0009492178445664895</v>
+        <v>0.000495382528248281</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.02004838362336159</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.038929812918968</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.101571866973333</v>
+        <v>0.6440095149754481</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0004664422986305992</v>
+        <v>0.0002422197419648264</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01311042439192533</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.038929812918968</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.101554932885094</v>
+        <v>0.6439982568560056</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0002686875277880244</v>
+        <v>0.0001385190694498177</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.05133971199393272</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.101625617644082</v>
+        <v>0.6440329452052312</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>8.651077467284822e-05</v>
+        <v>4.187137239341006e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.004720292985439301</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.3964372596156286</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.101529727587325</v>
+        <v>0.643980284750449</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>3.991582294542086e-05</v>
+        <v>1.970370261998147e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.009317035786807537</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.101525238428435</v>
+        <v>0.6439755581023584</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>1.946196130108506e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01496239006519318</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.101524421330565</v>
+        <v>0.6439727498763025</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>6.850902234816308e-06</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.009837927296757698</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.038929812918968</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.101518569280689</v>
+        <v>0.6439672843105835</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0350850522518158</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.038929812918968</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.101516796421636</v>
+        <v>0.6439638996921326</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.00524676451459527</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.038929812918968</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.10151079688804</v>
+        <v>0.6439582322618589</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.02020290121436119</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.038929812918968</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.101506554277886</v>
+        <v>0.6439586127969166</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.02062073349952698</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.038929812918968</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.101506782598921</v>
+        <v>0.6439588411179513</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.04520924761891365</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.038929812918968</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.101506872543571</v>
+        <v>0.6439589310626013</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.008843725547194481</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.038929812918968</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.101506014609986</v>
+        <v>0.6439580731290164</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.04590921476483345</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.038929812918968</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.101506242931021</v>
+        <v>0.6439583014500512</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.004830044694244862</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.101505447266809</v>
+        <v>0.6439575057858394</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.001541920937597752</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.101505509536182</v>
+        <v>0.6439575680552125</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.007703947834670544</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.101505537211459</v>
+        <v>0.6439575957304894</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01702291890978813</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.101505689425482</v>
+        <v>0.6439577479445127</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003587095998227596</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.10150534348452</v>
+        <v>0.6439574020035509</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.001521085388958454</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.101505419591532</v>
+        <v>0.6439574781105626</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01087530795484781</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.101505585643193</v>
+        <v>0.6439576441622241</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01946859434247017</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.101505945421793</v>
+        <v>0.6439580039408241</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01697504706680775</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.038929812918968</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.101505966178251</v>
+        <v>0.6439580246972819</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01366296969354153</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.038929812918968</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.101506069960539</v>
+        <v>0.6439581284795703</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.006688347086310387</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.038929812918968</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.101506298281574</v>
+        <v>0.6439583568006051</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.006188888102769852</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.038929812918968</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.101506173742828</v>
+        <v>0.6439582322618589</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.009111036546528339</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.038929812918968</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.101506201418105</v>
+        <v>0.6439582599371357</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0150569649413228</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.038929812918968</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.101506256768659</v>
+        <v>0.6439583152876897</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01973359286785126</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.038929812918968</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.101506519683789</v>
+        <v>0.6439585782028204</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01572014391422272</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.101506436657959</v>
+        <v>0.6439584951769896</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.007073541171848774</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.101506229093382</v>
+        <v>0.6439582876124128</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.0083127086982131</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.101506242931021</v>
+        <v>0.6439583014500512</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01565215736627579</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.101506381307405</v>
+        <v>0.6439584398264359</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.0120298694819212</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.101506097635816</v>
+        <v>0.6439581561548472</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.008364926092326641</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.101505924665336</v>
+        <v>0.6439579831843665</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.007801592350006104</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.101505820883047</v>
+        <v>0.6439578794020779</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.002446605823934078</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.101505966178251</v>
+        <v>0.6439580246972819</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.009817800484597683</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8389298129189675</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.101506208336924</v>
+        <v>0.6439582668559551</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.01775570958852768</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.101506035366443</v>
+        <v>0.6439580938854741</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.003451392985880375</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.16</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.101505737857216</v>
+        <v>0.6439577963762472</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.0227896086871624</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.101505724019578</v>
+        <v>0.6439577825386087</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.002167047001421452</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.101505357322158</v>
+        <v>0.6439574158411895</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.003594357520341873</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8389298129189675</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.101505357322158</v>
+        <v>0.6439574158411895</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.01308010146021843</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.101505295052785</v>
+        <v>0.6439573535718164</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.004730670712888241</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.101505191270497</v>
+        <v>0.6439572497895278</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.002026104368269444</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.101505018300016</v>
+        <v>0.6439570768190471</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.01015536952763796</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.101505066731751</v>
+        <v>0.6439571252507816</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.0006066644564270973</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.101504706953151</v>
+        <v>0.6439567654721816</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002427755855023861</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.101504665440235</v>
+        <v>0.6439567239592662</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.001088802702724934</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.101504720790789</v>
+        <v>0.6439567793098199</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.00307028740644455</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.101504776141343</v>
+        <v>0.6439568346603739</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.003782511688768864</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.101504817654259</v>
+        <v>0.6439568761732892</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.004953129217028618</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.3964372596156286</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.101504547820308</v>
+        <v>0.6439566063393392</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002641454339027405</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.3964372596156286</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.101504603170862</v>
+        <v>0.6439566616898931</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.0001727798953652382</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.101504748466066</v>
+        <v>0.6439568069850971</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.00463569164276123</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1964372596156286</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.10150471387197</v>
+        <v>0.6439567723910008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.00294551532715559</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1964372596156286</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.101504700034331</v>
+        <v>0.6439567585533622</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.006604137364774942</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.038929812918968</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.101504789978981</v>
+        <v>0.6439568484980124</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01876748725771904</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.3964372596156286</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.101505108244666</v>
+        <v>0.6439571667636971</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01496698427945375</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.2460552936877103</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.101504928355366</v>
+        <v>0.643956986874397</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.0007458683103322983</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.101504969868281</v>
+        <v>0.6439570283873123</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.004964102990925312</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.101504783060162</v>
+        <v>0.643956841579193</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.002411151304841042</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.101504852248354</v>
+        <v>0.6439569107673855</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.001009376719594002</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4460552936877104</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.101504651602597</v>
+        <v>0.6439567101216277</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.00204074289649725</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.101504693115512</v>
+        <v>0.643956751634543</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002486844547092915</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.088547846991049</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.101504720790789</v>
+        <v>0.6439567793098199</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_1_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_1_000006.xlsx
@@ -51029,7 +51029,7 @@
         <v>0.05133971199393272</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC63" t="n">
         <v>0.6440329452052312</v>
@@ -51824,7 +51824,7 @@
         <v>-0.004720292985439301</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1600000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
         <v>0.643980284750449</v>
@@ -52619,7 +52619,7 @@
         <v>0.009317035786807537</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0.6439755581023584</v>
@@ -53414,7 +53414,7 @@
         <v>0.01496239006519318</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0.6439727498763025</v>
@@ -54209,7 +54209,7 @@
         <v>0.009837927296757698</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0.6439672843105835</v>
@@ -56594,7 +56594,7 @@
         <v>0.02020290121436119</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.02000000000000007</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0.6439586127969166</v>
@@ -61364,7 +61364,7 @@
         <v>0.001541920937597752</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0.6439575680552125</v>
@@ -62159,7 +62159,7 @@
         <v>0.007703947834670544</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0.6439575957304894</v>
@@ -62954,7 +62954,7 @@
         <v>0.01702291890978813</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0.6439577479445127</v>
@@ -63749,7 +63749,7 @@
         <v>-0.003587095998227596</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0.6439574020035509</v>
@@ -64544,7 +64544,7 @@
         <v>0.001521085388958454</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0.6439574781105626</v>
@@ -68519,7 +68519,7 @@
         <v>0.006688347086310387</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0.6439583568006051</v>
